--- a/Compititor's_Price/Novia_Prices/Novia_Prices_08-04-2026.xlsx
+++ b/Compititor's_Price/Novia_Prices/Novia_Prices_08-04-2026.xlsx
@@ -826,7 +826,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>£78.81</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://diybuildingsupplies.co.uk/products/novia-vc200-reflective-air-leakage-vapour-control-layer-1-5m-x-50m-75m2?variant=50011861647678</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>£47.38</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>£47.38</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>£7.2</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>£72.0</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>£7.2</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>£19.27</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>£5.47</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>£86.85</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">

--- a/Compititor's_Price/Novia_Prices/Novia_Prices_08-04-2026.xlsx
+++ b/Compititor's_Price/Novia_Prices/Novia_Prices_08-04-2026.xlsx
@@ -784,7 +784,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£83.25</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Error: 503 Server Error: Service Unavailable for url: https://diybuildingsupplies.co.uk/products/novia-vc200-reflective-air-leakage-vapour-control-layer-1-5m-x-50m-75m2?variant=50011861647678</t>
+          <t>£78.81</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://build4less.co.uk/products/novia-black-pro-roof-and-wall-breather-membrane</t>
+          <t>No Link</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://build4less.co.uk/products/novia-black-pro-roof-and-wall-breather-membrane?variant=48536065999041</t>
+          <t>No Link</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>£40.94</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>£7.2</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>£144.0</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>£7.2</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>£72.0</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>£7.2</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>£12.0</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>£19.27</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>£5.47</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">

--- a/Compititor's_Price/Novia_Prices/Novia_Prices_08-04-2026.xlsx
+++ b/Compititor's_Price/Novia_Prices/Novia_Prices_08-04-2026.xlsx
@@ -784,7 +784,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>£83.25</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>£47.38</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>£40.88</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://build4less.co.uk/products/novia-black-supreme-all-sizes?variant=48088737743041</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>£40.94</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>£47.10</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://build4less.co.uk/products/noiva-black-pro-roof-and-wall-breather-membrane-all-sizes?variant=54891329945987</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>£67.10</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://build4less.co.uk/products/noiva-black-pro-roof-and-wall-breather-membrane-all-sizes?variant=54891329913219</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>£144.0</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>£7.2</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>£7.2</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>£12.0</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>£19.27</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>£19.27</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>£5.47</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>£5.47</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>£86.85</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
